--- a/R/translation/translation_data.xlsx
+++ b/R/translation/translation_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentturmine/Documents/GitHub/trust-index/R/base/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentturmine/Documents/GitHub/trust-index/R/translation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38322004-7FF6-2A43-8B7C-4B978D279A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5062AE6A-7DB2-A942-BB09-1C053F4094AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12240" yWindow="660" windowWidth="29400" windowHeight="17460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="translation_data" sheetId="1" r:id="rId1"/>
@@ -2531,15 +2531,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="27.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="27.6640625" style="4"/>
-    <col min="3" max="5" width="46.6640625" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="27.6640625" style="4"/>
+    <col min="3" max="6" width="46.6640625" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="27.6640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2555,14 +2555,15 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="1"/>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -2578,14 +2579,15 @@
       <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="3"/>
+      <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -2601,14 +2603,15 @@
       <c r="E3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
@@ -2624,14 +2627,15 @@
       <c r="E4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
@@ -2647,14 +2651,15 @@
       <c r="E5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
@@ -2670,14 +2675,15 @@
       <c r="E6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="3"/>
+      <c r="G6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>34</v>
       </c>
@@ -2693,14 +2699,15 @@
       <c r="E7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="3"/>
+      <c r="G7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
@@ -2716,14 +2723,15 @@
       <c r="E8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>42</v>
       </c>
@@ -2739,14 +2747,15 @@
       <c r="E9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>48</v>
       </c>
@@ -2762,14 +2771,15 @@
       <c r="E10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>53</v>
       </c>
@@ -2785,14 +2795,15 @@
       <c r="E11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="3"/>
+      <c r="G11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>59</v>
       </c>
@@ -2808,14 +2819,15 @@
       <c r="E12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="3"/>
+      <c r="G12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>63</v>
       </c>
@@ -2831,14 +2843,15 @@
       <c r="E13" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="3"/>
+      <c r="G13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>67</v>
       </c>
@@ -2856,8 +2869,9 @@
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>72</v>
       </c>
@@ -2875,8 +2889,9 @@
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>76</v>
       </c>
@@ -2894,8 +2909,9 @@
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>79</v>
       </c>
@@ -2911,10 +2927,11 @@
       <c r="E17" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F17" s="3"/>
+      <c r="F17" s="5"/>
       <c r="G17" s="3"/>
-    </row>
-    <row r="18" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>83</v>
       </c>
@@ -2930,10 +2947,11 @@
       <c r="E18" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F18" s="3"/>
+      <c r="F18" s="5"/>
       <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>87</v>
       </c>
@@ -2949,10 +2967,11 @@
       <c r="E19" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F19" s="3"/>
+      <c r="F19" s="5"/>
       <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>91</v>
       </c>
@@ -2968,10 +2987,11 @@
       <c r="E20" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F20" s="3"/>
+      <c r="F20" s="5"/>
       <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>95</v>
       </c>
@@ -2987,10 +3007,11 @@
       <c r="E21" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F21" s="3"/>
+      <c r="F21" s="5"/>
       <c r="G21" s="3"/>
-    </row>
-    <row r="22" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>99</v>
       </c>
@@ -3006,10 +3027,11 @@
       <c r="E22" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F22" s="3"/>
+      <c r="F22" s="5"/>
       <c r="G22" s="3"/>
-    </row>
-    <row r="23" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>103</v>
       </c>
@@ -3025,10 +3047,11 @@
       <c r="E23" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F23" s="3"/>
+      <c r="F23" s="5"/>
       <c r="G23" s="3"/>
-    </row>
-    <row r="24" spans="1:7" ht="119" x14ac:dyDescent="0.2">
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:8" ht="119" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>107</v>
       </c>
@@ -3044,10 +3067,11 @@
       <c r="E24" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="F24" s="3"/>
+      <c r="F24" s="5"/>
       <c r="G24" s="3"/>
-    </row>
-    <row r="25" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>111</v>
       </c>
@@ -3063,10 +3087,11 @@
       <c r="E25" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F25" s="3"/>
+      <c r="F25" s="5"/>
       <c r="G25" s="3"/>
-    </row>
-    <row r="26" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>115</v>
       </c>
@@ -3082,10 +3107,11 @@
       <c r="E26" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F26" s="3"/>
+      <c r="F26" s="5"/>
       <c r="G26" s="3"/>
-    </row>
-    <row r="27" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>119</v>
       </c>
@@ -3101,10 +3127,11 @@
       <c r="E27" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="F27" s="3"/>
+      <c r="F27" s="5"/>
       <c r="G27" s="3"/>
-    </row>
-    <row r="28" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>123</v>
       </c>
@@ -3120,10 +3147,11 @@
       <c r="E28" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F28" s="3"/>
+      <c r="F28" s="5"/>
       <c r="G28" s="3"/>
-    </row>
-    <row r="29" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>127</v>
       </c>
@@ -3139,10 +3167,11 @@
       <c r="E29" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F29" s="3"/>
+      <c r="F29" s="5"/>
       <c r="G29" s="3"/>
-    </row>
-    <row r="30" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>131</v>
       </c>
@@ -3158,10 +3187,11 @@
       <c r="E30" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="F30" s="3"/>
+      <c r="F30" s="5"/>
       <c r="G30" s="3"/>
-    </row>
-    <row r="31" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H30" s="3"/>
+    </row>
+    <row r="31" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>134</v>
       </c>
@@ -3177,10 +3207,11 @@
       <c r="E31" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F31" s="3"/>
+      <c r="F31" s="5"/>
       <c r="G31" s="3"/>
-    </row>
-    <row r="32" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>138</v>
       </c>
@@ -3196,10 +3227,11 @@
       <c r="E32" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="F32" s="3"/>
+      <c r="F32" s="5"/>
       <c r="G32" s="3"/>
-    </row>
-    <row r="33" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>142</v>
       </c>
@@ -3215,10 +3247,11 @@
       <c r="E33" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="F33" s="3"/>
+      <c r="F33" s="5"/>
       <c r="G33" s="3"/>
-    </row>
-    <row r="34" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>146</v>
       </c>
@@ -3234,10 +3267,11 @@
       <c r="E34" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="F34" s="3"/>
+      <c r="F34" s="5"/>
       <c r="G34" s="3"/>
-    </row>
-    <row r="35" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H34" s="3"/>
+    </row>
+    <row r="35" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>150</v>
       </c>
@@ -3253,10 +3287,11 @@
       <c r="E35" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F35" s="3"/>
+      <c r="F35" s="5"/>
       <c r="G35" s="3"/>
-    </row>
-    <row r="36" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>154</v>
       </c>
@@ -3272,10 +3307,11 @@
       <c r="E36" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="F36" s="3"/>
+      <c r="F36" s="5"/>
       <c r="G36" s="3"/>
-    </row>
-    <row r="37" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>158</v>
       </c>
@@ -3291,10 +3327,11 @@
       <c r="E37" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="F37" s="3"/>
+      <c r="F37" s="5"/>
       <c r="G37" s="3"/>
-    </row>
-    <row r="38" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>162</v>
       </c>
@@ -3310,10 +3347,11 @@
       <c r="E38" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="F38" s="3"/>
+      <c r="F38" s="5"/>
       <c r="G38" s="3"/>
-    </row>
-    <row r="39" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>166</v>
       </c>
@@ -3329,10 +3367,11 @@
       <c r="E39" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F39" s="3"/>
+      <c r="F39" s="5"/>
       <c r="G39" s="3"/>
-    </row>
-    <row r="40" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>170</v>
       </c>
@@ -3348,10 +3387,11 @@
       <c r="E40" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="F40" s="3"/>
+      <c r="F40" s="5"/>
       <c r="G40" s="3"/>
-    </row>
-    <row r="41" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>174</v>
       </c>
@@ -3367,10 +3407,11 @@
       <c r="E41" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="F41" s="3"/>
+      <c r="F41" s="5"/>
       <c r="G41" s="3"/>
-    </row>
-    <row r="42" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>178</v>
       </c>
@@ -3386,10 +3427,11 @@
       <c r="E42" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="F42" s="3"/>
+      <c r="F42" s="5"/>
       <c r="G42" s="3"/>
-    </row>
-    <row r="43" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>182</v>
       </c>
@@ -3405,10 +3447,11 @@
       <c r="E43" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F43" s="3"/>
+      <c r="F43" s="5"/>
       <c r="G43" s="3"/>
-    </row>
-    <row r="44" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>186</v>
       </c>
@@ -3426,8 +3469,9 @@
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
-    </row>
-    <row r="45" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>188</v>
       </c>
@@ -3443,14 +3487,15 @@
       <c r="E45" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="3"/>
+      <c r="G45" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="H45" s="3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>193</v>
       </c>
@@ -3466,14 +3511,15 @@
       <c r="E46" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="F46" s="3"/>
+      <c r="G46" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="H46" s="3" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>197</v>
       </c>
@@ -3489,14 +3535,15 @@
       <c r="E47" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="3"/>
+      <c r="G47" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="H47" s="3" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>202</v>
       </c>
@@ -3512,14 +3559,15 @@
       <c r="E48" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F48" s="3"/>
+      <c r="G48" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="H48" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>207</v>
       </c>
@@ -3535,14 +3583,15 @@
       <c r="E49" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F49" s="3"/>
+      <c r="G49" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="H49" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>212</v>
       </c>
@@ -3558,14 +3607,15 @@
       <c r="E50" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="F50" s="3"/>
+      <c r="G50" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="H50" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>214</v>
       </c>
@@ -3581,14 +3631,15 @@
       <c r="E51" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="3"/>
+      <c r="G51" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="H51" s="3" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>219</v>
       </c>
@@ -3604,14 +3655,15 @@
       <c r="E52" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="3"/>
+      <c r="G52" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="H52" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>224</v>
       </c>
@@ -3627,14 +3679,15 @@
       <c r="E53" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="3"/>
+      <c r="G53" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="H53" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>228</v>
       </c>
@@ -3650,14 +3703,15 @@
       <c r="E54" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="F54" s="3"/>
+      <c r="G54" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="H54" s="3" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>233</v>
       </c>
@@ -3673,14 +3727,15 @@
       <c r="E55" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="F55" s="3" t="s">
+      <c r="F55" s="3"/>
+      <c r="G55" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="H55" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>238</v>
       </c>
@@ -3696,14 +3751,15 @@
       <c r="E56" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="F56" s="3" t="s">
+      <c r="F56" s="3"/>
+      <c r="G56" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G56" s="3" t="s">
+      <c r="H56" s="3" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>243</v>
       </c>
@@ -3719,14 +3775,15 @@
       <c r="E57" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F57" s="3"/>
+      <c r="G57" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="H57" s="3" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>248</v>
       </c>
@@ -3742,14 +3799,15 @@
       <c r="E58" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="F58" s="3"/>
+      <c r="G58" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="H58" s="3" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>253</v>
       </c>
@@ -3765,14 +3823,15 @@
       <c r="E59" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="F59" s="3"/>
+      <c r="G59" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="H59" s="3" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>258</v>
       </c>
@@ -3788,14 +3847,15 @@
       <c r="E60" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="F60" s="3"/>
+      <c r="G60" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G60" s="3" t="s">
+      <c r="H60" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>263</v>
       </c>
@@ -3811,14 +3871,15 @@
       <c r="E61" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F61" s="3" t="s">
+      <c r="F61" s="3"/>
+      <c r="G61" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="H61" s="3" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>265</v>
       </c>
@@ -3834,14 +3895,15 @@
       <c r="E62" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="F62" s="3"/>
+      <c r="G62" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="H62" s="3" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>269</v>
       </c>
@@ -3857,14 +3919,15 @@
       <c r="E63" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F63" s="3" t="s">
+      <c r="F63" s="3"/>
+      <c r="G63" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="H63" s="3" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>273</v>
       </c>
@@ -3880,14 +3943,15 @@
       <c r="E64" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="F64" s="3"/>
+      <c r="G64" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="H64" s="3" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>278</v>
       </c>
@@ -3903,14 +3967,15 @@
       <c r="E65" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="3"/>
+      <c r="G65" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="H65" s="3" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>282</v>
       </c>
@@ -3926,14 +3991,15 @@
       <c r="E66" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="F66" s="3"/>
+      <c r="G66" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="H66" s="3" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>288</v>
       </c>
@@ -3949,14 +4015,15 @@
       <c r="E67" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F67" s="3"/>
+      <c r="G67" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="H67" s="3" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>292</v>
       </c>
@@ -3972,14 +4039,15 @@
       <c r="E68" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F68" s="3"/>
+      <c r="G68" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="H68" s="3" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>298</v>
       </c>
@@ -3995,14 +4063,15 @@
       <c r="E69" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="F69" s="3"/>
+      <c r="G69" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="H69" s="3" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>302</v>
       </c>
@@ -4018,14 +4087,15 @@
       <c r="E70" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="F70" s="3"/>
+      <c r="G70" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="H70" s="3" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>308</v>
       </c>
@@ -4041,14 +4111,15 @@
       <c r="E71" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="F71" s="3"/>
+      <c r="G71" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="H71" s="3" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>313</v>
       </c>
@@ -4064,14 +4135,15 @@
       <c r="E72" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="F72" s="3"/>
+      <c r="G72" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="H72" s="3" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>319</v>
       </c>
@@ -4087,14 +4159,15 @@
       <c r="E73" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="F73" s="3"/>
+      <c r="G73" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="G73" s="3" t="s">
+      <c r="H73" s="3" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>324</v>
       </c>
@@ -4110,14 +4183,15 @@
       <c r="E74" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="F74" s="3" t="s">
+      <c r="F74" s="3"/>
+      <c r="G74" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="G74" s="3" t="s">
+      <c r="H74" s="3" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>330</v>
       </c>
@@ -4133,14 +4207,15 @@
       <c r="E75" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="F75" s="3" t="s">
+      <c r="F75" s="3"/>
+      <c r="G75" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="H75" s="3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>335</v>
       </c>
@@ -4156,10 +4231,11 @@
       <c r="E76" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="F76" s="3"/>
+      <c r="F76" s="5"/>
       <c r="G76" s="3"/>
-    </row>
-    <row r="77" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H76" s="3"/>
+    </row>
+    <row r="77" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>339</v>
       </c>
@@ -4175,10 +4251,11 @@
       <c r="E77" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="F77" s="3"/>
+      <c r="F77" s="5"/>
       <c r="G77" s="3"/>
-    </row>
-    <row r="78" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H77" s="3"/>
+    </row>
+    <row r="78" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
         <v>343</v>
       </c>
@@ -4194,10 +4271,11 @@
       <c r="E78" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="F78" s="3"/>
+      <c r="F78" s="5"/>
       <c r="G78" s="3"/>
-    </row>
-    <row r="79" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H78" s="3"/>
+    </row>
+    <row r="79" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>347</v>
       </c>
@@ -4213,10 +4291,11 @@
       <c r="E79" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="F79" s="3"/>
+      <c r="F79" s="5"/>
       <c r="G79" s="3"/>
-    </row>
-    <row r="80" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="H79" s="3"/>
+    </row>
+    <row r="80" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
         <v>351</v>
       </c>
@@ -4232,14 +4311,15 @@
       <c r="E80" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="F80" s="3"/>
+      <c r="G80" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G80" s="3" t="s">
+      <c r="H80" s="3" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
         <v>357</v>
       </c>
@@ -4255,14 +4335,15 @@
       <c r="E81" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="F81" s="3"/>
+      <c r="G81" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G81" s="3" t="s">
+      <c r="H81" s="3" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>361</v>
       </c>
@@ -4278,14 +4359,15 @@
       <c r="E82" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F82" s="3"/>
+      <c r="G82" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G82" s="3" t="s">
+      <c r="H82" s="3" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
         <v>366</v>
       </c>
@@ -4301,14 +4383,15 @@
       <c r="E83" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="F83" s="3"/>
+      <c r="G83" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="G83" s="3" t="s">
+      <c r="H83" s="3" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
         <v>371</v>
       </c>
@@ -4324,14 +4407,15 @@
       <c r="E84" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="F84" s="3" t="s">
+      <c r="F84" s="3"/>
+      <c r="G84" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G84" s="3" t="s">
+      <c r="H84" s="3" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
         <v>376</v>
       </c>
@@ -4347,14 +4431,15 @@
       <c r="E85" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="F85" s="3"/>
+      <c r="G85" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G85" s="3" t="s">
+      <c r="H85" s="3" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
         <v>380</v>
       </c>
@@ -4370,14 +4455,15 @@
       <c r="E86" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="F86" s="3" t="s">
+      <c r="F86" s="3"/>
+      <c r="G86" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G86" s="3" t="s">
+      <c r="H86" s="3" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
         <v>384</v>
       </c>
@@ -4393,14 +4479,15 @@
       <c r="E87" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F87" s="3"/>
+      <c r="G87" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G87" s="3" t="s">
+      <c r="H87" s="3" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
         <v>388</v>
       </c>
@@ -4416,14 +4503,15 @@
       <c r="E88" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="F88" s="3" t="s">
+      <c r="F88" s="3"/>
+      <c r="G88" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G88" s="3" t="s">
+      <c r="H88" s="3" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
         <v>392</v>
       </c>
@@ -4439,14 +4527,15 @@
       <c r="E89" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="F89" s="3" t="s">
+      <c r="F89" s="3"/>
+      <c r="G89" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G89" s="3" t="s">
+      <c r="H89" s="3" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
         <v>397</v>
       </c>
@@ -4462,14 +4551,15 @@
       <c r="E90" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="F90" s="3"/>
+      <c r="G90" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G90" s="3" t="s">
+      <c r="H90" s="3" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>401</v>
       </c>
@@ -4485,14 +4575,15 @@
       <c r="E91" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="F91" s="3"/>
+      <c r="G91" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="H91" s="3" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>406</v>
       </c>
@@ -4508,14 +4599,15 @@
       <c r="E92" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="F92" s="3" t="s">
+      <c r="F92" s="3"/>
+      <c r="G92" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G92" s="3" t="s">
+      <c r="H92" s="3" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
         <v>411</v>
       </c>
@@ -4531,14 +4623,15 @@
       <c r="E93" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F93" s="3"/>
+      <c r="G93" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G93" s="3" t="s">
+      <c r="H93" s="3" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
         <v>415</v>
       </c>
@@ -4554,14 +4647,15 @@
       <c r="E94" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="F94" s="3" t="s">
+      <c r="F94" s="3"/>
+      <c r="G94" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="H94" s="3" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
         <v>419</v>
       </c>
@@ -4577,14 +4671,15 @@
       <c r="E95" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="F95" s="3" t="s">
+      <c r="F95" s="3"/>
+      <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="H95" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
         <v>423</v>
       </c>
@@ -4600,14 +4695,15 @@
       <c r="E96" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="F96" s="3"/>
+      <c r="G96" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="H96" s="3" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
         <v>429</v>
       </c>
@@ -4623,14 +4719,15 @@
       <c r="E97" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="F97" s="3"/>
+      <c r="G97" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="G97" s="3" t="s">
+      <c r="H97" s="3" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
         <v>433</v>
       </c>
@@ -4646,14 +4743,15 @@
       <c r="E98" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="F98" s="3" t="s">
+      <c r="F98" s="3"/>
+      <c r="G98" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="G98" s="3" t="s">
+      <c r="H98" s="3" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
         <v>437</v>
       </c>
@@ -4669,14 +4767,15 @@
       <c r="E99" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="F99" s="3" t="s">
+      <c r="F99" s="3"/>
+      <c r="G99" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G99" s="3" t="s">
+      <c r="H99" s="3" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
         <v>442</v>
       </c>
@@ -4692,14 +4791,15 @@
       <c r="E100" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="F100" s="3" t="s">
+      <c r="F100" s="3"/>
+      <c r="G100" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G100" s="3" t="s">
+      <c r="H100" s="3" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
         <v>447</v>
       </c>
@@ -4715,14 +4815,15 @@
       <c r="E101" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="F101" s="3"/>
+      <c r="G101" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="H101" s="3" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
         <v>452</v>
       </c>
@@ -4738,14 +4839,15 @@
       <c r="E102" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="F102" s="3" t="s">
+      <c r="F102" s="3"/>
+      <c r="G102" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="G102" s="3" t="s">
+      <c r="H102" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
         <v>457</v>
       </c>
@@ -4761,14 +4863,15 @@
       <c r="E103" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="F103" s="3" t="s">
+      <c r="F103" s="3"/>
+      <c r="G103" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="G103" s="3" t="s">
+      <c r="H103" s="3" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>463</v>
       </c>
@@ -4784,14 +4887,15 @@
       <c r="E104" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="F104" s="3" t="s">
+      <c r="F104" s="3"/>
+      <c r="G104" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="G104" s="3" t="s">
+      <c r="H104" s="3" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
         <v>468</v>
       </c>
@@ -4807,14 +4911,15 @@
       <c r="E105" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="F105" s="3" t="s">
+      <c r="F105" s="3"/>
+      <c r="G105" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="G105" s="3" t="s">
+      <c r="H105" s="3" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
         <v>472</v>
       </c>
@@ -4830,14 +4935,15 @@
       <c r="E106" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="F106" s="3" t="s">
+      <c r="F106" s="3"/>
+      <c r="G106" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="G106" s="3" t="s">
+      <c r="H106" s="3" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>476</v>
       </c>
@@ -4853,14 +4959,15 @@
       <c r="E107" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="F107" s="3" t="s">
+      <c r="F107" s="3"/>
+      <c r="G107" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="G107" s="3" t="s">
+      <c r="H107" s="3" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
         <v>477</v>
       </c>
@@ -4876,14 +4983,15 @@
       <c r="E108" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="F108" s="3" t="s">
+      <c r="F108" s="3"/>
+      <c r="G108" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="G108" s="3" t="s">
+      <c r="H108" s="3" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
         <v>481</v>
       </c>
@@ -4899,14 +5007,15 @@
       <c r="E109" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="F109" s="3" t="s">
+      <c r="F109" s="3"/>
+      <c r="G109" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="G109" s="3" t="s">
+      <c r="H109" s="3" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
         <v>486</v>
       </c>
@@ -4922,14 +5031,15 @@
       <c r="E110" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="F110" s="3" t="s">
+      <c r="F110" s="3"/>
+      <c r="G110" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="G110" s="3" t="s">
+      <c r="H110" s="3" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
         <v>492</v>
       </c>
@@ -4945,14 +5055,15 @@
       <c r="E111" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="F111" s="3" t="s">
+      <c r="F111" s="3"/>
+      <c r="G111" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="G111" s="3" t="s">
+      <c r="H111" s="3" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
         <v>498</v>
       </c>
@@ -4968,14 +5079,15 @@
       <c r="E112" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="F112" s="3" t="s">
+      <c r="F112" s="3"/>
+      <c r="G112" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="G112" s="3" t="s">
+      <c r="H112" s="3" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>503</v>
       </c>
@@ -4991,14 +5103,15 @@
       <c r="E113" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="F113" s="3" t="s">
+      <c r="F113" s="3"/>
+      <c r="G113" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G113" s="3" t="s">
+      <c r="H113" s="3" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>507</v>
       </c>
@@ -5014,14 +5127,15 @@
       <c r="E114" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="F114" s="3" t="s">
+      <c r="F114" s="3"/>
+      <c r="G114" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="G114" s="3" t="s">
+      <c r="H114" s="3" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>511</v>
       </c>
@@ -5037,14 +5151,15 @@
       <c r="E115" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="F115" s="3" t="s">
+      <c r="F115" s="3"/>
+      <c r="G115" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G115" s="3" t="s">
+      <c r="H115" s="3" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
         <v>516</v>
       </c>
@@ -5060,14 +5175,15 @@
       <c r="E116" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="F116" s="3" t="s">
+      <c r="F116" s="3"/>
+      <c r="G116" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G116" s="3" t="s">
+      <c r="H116" s="3" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
         <v>518</v>
       </c>
@@ -5083,14 +5199,15 @@
       <c r="E117" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="F117" s="3" t="s">
+      <c r="F117" s="3"/>
+      <c r="G117" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G117" s="3" t="s">
+      <c r="H117" s="3" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
         <v>520</v>
       </c>
@@ -5106,14 +5223,15 @@
       <c r="E118" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="F118" s="3" t="s">
+      <c r="F118" s="3"/>
+      <c r="G118" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G118" s="3" t="s">
+      <c r="H118" s="3" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
         <v>522</v>
       </c>
@@ -5129,14 +5247,15 @@
       <c r="E119" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="F119" s="3" t="s">
+      <c r="F119" s="3"/>
+      <c r="G119" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G119" s="3" t="s">
+      <c r="H119" s="3" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>524</v>
       </c>
@@ -5152,14 +5271,15 @@
       <c r="E120" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="F120" s="3" t="s">
+      <c r="F120" s="3"/>
+      <c r="G120" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G120" s="3" t="s">
+      <c r="H120" s="3" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>526</v>
       </c>
@@ -5175,14 +5295,15 @@
       <c r="E121" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="F121" s="3" t="s">
+      <c r="F121" s="3"/>
+      <c r="G121" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G121" s="3" t="s">
+      <c r="H121" s="3" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
         <v>530</v>
       </c>
@@ -5198,14 +5319,15 @@
       <c r="E122" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="F122" s="3" t="s">
+      <c r="F122" s="3"/>
+      <c r="G122" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G122" s="3" t="s">
+      <c r="H122" s="3" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
         <v>533</v>
       </c>
@@ -5221,14 +5343,15 @@
       <c r="E123" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="F123" s="3" t="s">
+      <c r="F123" s="3"/>
+      <c r="G123" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G123" s="3" t="s">
+      <c r="H123" s="3" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
         <v>536</v>
       </c>
@@ -5244,14 +5367,15 @@
       <c r="E124" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="F124" s="3" t="s">
+      <c r="F124" s="3"/>
+      <c r="G124" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G124" s="3" t="s">
+      <c r="H124" s="3" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
         <v>540</v>
       </c>
@@ -5267,14 +5391,15 @@
       <c r="E125" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="F125" s="3" t="s">
+      <c r="F125" s="3"/>
+      <c r="G125" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G125" s="3" t="s">
+      <c r="H125" s="3" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
         <v>545</v>
       </c>
@@ -5290,14 +5415,15 @@
       <c r="E126" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="F126" s="3" t="s">
+      <c r="F126" s="3"/>
+      <c r="G126" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G126" s="3" t="s">
+      <c r="H126" s="3" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
         <v>549</v>
       </c>
@@ -5313,14 +5439,15 @@
       <c r="E127" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="F127" s="3" t="s">
+      <c r="F127" s="3"/>
+      <c r="G127" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G127" s="3" t="s">
+      <c r="H127" s="3" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
         <v>553</v>
       </c>
@@ -5336,14 +5463,15 @@
       <c r="E128" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="F128" s="3" t="s">
+      <c r="F128" s="3"/>
+      <c r="G128" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G128" s="3" t="s">
+      <c r="H128" s="3" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
         <v>557</v>
       </c>
@@ -5359,14 +5487,15 @@
       <c r="E129" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="F129" s="3" t="s">
+      <c r="F129" s="3"/>
+      <c r="G129" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G129" s="3" t="s">
+      <c r="H129" s="3" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
         <v>561</v>
       </c>
@@ -5382,14 +5511,15 @@
       <c r="E130" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="F130" s="3" t="s">
+      <c r="F130" s="3"/>
+      <c r="G130" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G130" s="3" t="s">
+      <c r="H130" s="3" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
         <v>565</v>
       </c>
@@ -5405,14 +5535,15 @@
       <c r="E131" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="F131" s="3" t="s">
+      <c r="F131" s="3"/>
+      <c r="G131" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G131" s="3" t="s">
+      <c r="H131" s="3" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
         <v>569</v>
       </c>
@@ -5428,14 +5559,15 @@
       <c r="E132" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="F132" s="3" t="s">
+      <c r="F132" s="3"/>
+      <c r="G132" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G132" s="3" t="s">
+      <c r="H132" s="3" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
         <v>574</v>
       </c>
@@ -5451,14 +5583,15 @@
       <c r="E133" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="F133" s="3" t="s">
+      <c r="F133" s="3"/>
+      <c r="G133" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G133" s="3" t="s">
+      <c r="H133" s="3" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
         <v>578</v>
       </c>
@@ -5474,14 +5607,15 @@
       <c r="E134" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="F134" s="3" t="s">
+      <c r="F134" s="3"/>
+      <c r="G134" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G134" s="3" t="s">
+      <c r="H134" s="3" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
         <v>582</v>
       </c>
@@ -5497,10 +5631,11 @@
       <c r="E135" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="F135" s="3" t="s">
+      <c r="F135" s="3"/>
+      <c r="G135" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G135" s="3" t="s">
+      <c r="H135" s="3" t="s">
         <v>586</v>
       </c>
     </row>
